--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_model_effect.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_model_effect.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_model_effect" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="832">
   <si>
     <t>编号</t>
   </si>
@@ -2339,16 +2339,16 @@
     <t>星云火链1</t>
   </si>
   <si>
-    <t>Effect/Skill/xingyunhuolian</t>
+    <t>Effect/Skill/monster237_atk1</t>
+  </si>
+  <si>
+    <t>冲击波</t>
+  </si>
+  <si>
+    <t>Effect/Skill/chongji</t>
   </si>
   <si>
     <t>0#0#1</t>
-  </si>
-  <si>
-    <t>冲击波</t>
-  </si>
-  <si>
-    <t>Effect/Skill/chongji</t>
   </si>
   <si>
     <t>致命圣印施法</t>
@@ -3628,6 +3628,12 @@
   </si>
   <si>
     <t>星云火链3</t>
+  </si>
+  <si>
+    <t>Effect/Skill/xingyunhuolian</t>
+  </si>
+  <si>
+    <t>monster237_atk1</t>
   </si>
 </sst>
 </file>
@@ -15180,27 +15186,21 @@
         <v>510</v>
       </c>
       <c r="D257" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F257" s="1">
-        <v>5</v>
-      </c>
-      <c r="G257" s="1">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G257" s="1"/>
       <c r="H257" s="1"/>
       <c r="I257" s="1">
-        <v>2500</v>
-      </c>
-      <c r="J257" s="1">
-        <v>1</v>
-      </c>
-      <c r="K257" s="1" t="s">
-        <v>511</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
       <c r="L257" s="2"/>
       <c r="M257" s="1" t="s">
         <v>18</v>
@@ -15216,10 +15216,10 @@
         <v>6003</v>
       </c>
       <c r="B258" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="D258" s="1">
         <v>500</v>
@@ -15240,7 +15240,7 @@
         <v>1</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L258" s="2"/>
       <c r="M258" s="1" t="s">
@@ -16630,7 +16630,7 @@
         <v>586</v>
       </c>
       <c r="D295" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>54</v>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="H295" s="1"/>
       <c r="I295" s="1">
-        <v>3400</v>
+        <v>6800</v>
       </c>
       <c r="J295" s="1"/>
       <c r="K295" s="1"/>
@@ -16663,7 +16663,7 @@
         <v>586</v>
       </c>
       <c r="D296" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>54</v>
@@ -16672,7 +16672,7 @@
       <c r="G296" s="1"/>
       <c r="H296" s="1"/>
       <c r="I296" s="1">
-        <v>5100</v>
+        <v>8500</v>
       </c>
       <c r="J296" s="1"/>
       <c r="K296" s="1"/>
@@ -16692,7 +16692,7 @@
         <v>586</v>
       </c>
       <c r="D297" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>54</v>
@@ -16701,7 +16701,7 @@
       <c r="G297" s="1"/>
       <c r="H297" s="1"/>
       <c r="I297" s="1">
-        <v>6800</v>
+        <v>10200</v>
       </c>
       <c r="J297" s="1"/>
       <c r="K297" s="1"/>
@@ -16721,7 +16721,7 @@
         <v>586</v>
       </c>
       <c r="D298" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>54</v>
@@ -16730,7 +16730,7 @@
       <c r="G298" s="1"/>
       <c r="H298" s="1"/>
       <c r="I298" s="1">
-        <v>8500</v>
+        <v>11900</v>
       </c>
       <c r="J298" s="1"/>
       <c r="K298" s="1"/>
@@ -16750,7 +16750,7 @@
         <v>586</v>
       </c>
       <c r="D299" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>54</v>
@@ -16759,7 +16759,7 @@
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
       <c r="I299" s="1">
-        <v>10200</v>
+        <v>13600</v>
       </c>
       <c r="J299" s="1"/>
       <c r="K299" s="1"/>
@@ -16779,7 +16779,7 @@
         <v>586</v>
       </c>
       <c r="D300" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>54</v>
@@ -16788,7 +16788,7 @@
       <c r="G300" s="1"/>
       <c r="H300" s="1"/>
       <c r="I300" s="1">
-        <v>11900</v>
+        <v>15800</v>
       </c>
       <c r="J300" s="1"/>
       <c r="K300" s="1"/>
@@ -16808,7 +16808,7 @@
         <v>586</v>
       </c>
       <c r="D301" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>54</v>
@@ -16817,7 +16817,7 @@
       <c r="G301" s="1"/>
       <c r="H301" s="1"/>
       <c r="I301" s="1">
-        <v>13600</v>
+        <v>19600</v>
       </c>
       <c r="J301" s="1"/>
       <c r="K301" s="1"/>
@@ -20166,8 +20166,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="1">
@@ -20257,7 +20257,7 @@
         <v>509</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>510</v>
+        <v>830</v>
       </c>
       <c r="D3" s="1">
         <v>1000</v>
@@ -20278,7 +20278,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="1" t="s">
@@ -20288,6 +20288,11 @@
         <v>18</v>
       </c>
       <c r="O3" s="2"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" t="s">
+        <v>831</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
